--- a/extenbooks/XS1304.xlsx
+++ b/extenbooks/XS1304.xlsx
@@ -1519,8 +1519,8 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1556,20 +1556,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>derive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>XS1301</t>
+          <t>XS1301, XS1201</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS1304-COMBINED</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>XS1304-A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>XS1304 = XS1301 - XS1201 (Moos NSW/GDP - ST NSW/GDP)</t>
+        </is>
+      </c>
     </row>
     <row r="3"/>
     <row r="4">

--- a/extenbooks/XS1304.xlsx
+++ b/extenbooks/XS1304.xlsx
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[internal-decision-record] (2026-05-06): ST2 P21 achieves 1959-1997 overlap mean NSW/GDP = 0.013, within 0.002 of Moos's published 0.011. The residual gap is attributable to NIPA vintage differences between our 2026 pull and Moos's ~2015 data. The V11 benchmark range for validation is [0.008, 0.018] — ST2 value of 0.013 passes. This is the primary validation criterion for XS1304.</t>
+          <t>[internal-decision-record] (2026-05-06): predecessor-build P21 achieves 1959-1997 overlap mean NSW/GDP = 0.013, within 0.002 of Moos's published 0.011. The residual gap is attributable to NIPA vintage differences between our 2026 pull and Moos's ~2015 data. The V11 benchmark range for validation is [0.008, 0.018] — predecessor-build value of 0.013 passes. This is the primary validation criterion for XS1304.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XS1304 is XS1301 restricted to 1959-1997, enabling direct comparison with ST 2002 coverage. Moos's replicated series shows mean 1.1% of GDP vs Shaikh-Tonak original mean 0.0% — difference attributed to post-1999 NIPA revision. ST2 achieves 0.013 vs Moos published 0.011, within V11 benchmark range [0.008, 0.018].</t>
+          <t>XS1304 is XS1301 restricted to 1959-1997, enabling direct comparison with ST 2002 coverage. Moos's replicated series shows mean 1.1% of GDP vs Shaikh-Tonak original mean 0.0% — difference attributed to post-1999 NIPA revision. predecessor-build achieves 0.013 vs Moos published 0.011, within V11 benchmark range [0.008, 0.018].</t>
         </is>
       </c>
     </row>
